--- a/artfynd/A 20407-2026 artfynd.xlsx
+++ b/artfynd/A 20407-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186483</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20407-2026 artfynd.xlsx
+++ b/artfynd/A 20407-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186483</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20407-2026 artfynd.xlsx
+++ b/artfynd/A 20407-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186483</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20407-2026 artfynd.xlsx
+++ b/artfynd/A 20407-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186483</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20407-2026 artfynd.xlsx
+++ b/artfynd/A 20407-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186483</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
